--- a/MPM/optim_on.xlsx
+++ b/MPM/optim_on.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N111"/>
+  <dimension ref="A1:P111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,16 @@
           <t>MPM_mean (0-255)</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>OT_mean</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>MPM_mean</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -530,7 +540,13 @@
         <v>86.74330999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>3938.852875536469</v>
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>189.5738271972594</v>
       </c>
     </row>
     <row r="3">
@@ -576,7 +592,13 @@
         <v>76.47727999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>3715.454639763967</v>
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>188.0262300557648</v>
       </c>
     </row>
     <row r="4">
@@ -622,7 +644,13 @@
         <v>81.66265</v>
       </c>
       <c r="N4" t="n">
-        <v>3648.957866268777</v>
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>186.3737289922344</v>
       </c>
     </row>
     <row r="5">
@@ -668,7 +696,13 @@
         <v>72.03362183754993</v>
       </c>
       <c r="N5" t="n">
-        <v>3665.777302047311</v>
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>192.0694746123999</v>
       </c>
     </row>
     <row r="6">
@@ -714,7 +748,13 @@
         <v>69.6571238348868</v>
       </c>
       <c r="N6" t="n">
-        <v>3880.757823535233</v>
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>193.0508933302714</v>
       </c>
     </row>
     <row r="7">
@@ -760,7 +800,13 @@
         <v>72.1260541500222</v>
       </c>
       <c r="N7" t="n">
-        <v>4022.12793290157</v>
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>192.2504772635029</v>
       </c>
     </row>
     <row r="8">
@@ -806,7 +852,13 @@
         <v>66.46690127449116</v>
       </c>
       <c r="N8" t="n">
-        <v>3901.731487117052</v>
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>192.2197670678557</v>
       </c>
     </row>
     <row r="9">
@@ -852,7 +904,13 @@
         <v>70.04945786570286</v>
       </c>
       <c r="N9" t="n">
-        <v>3643.771855793043</v>
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>192.5046271964567</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +956,13 @@
         <v>70.81282078413454</v>
       </c>
       <c r="N10" t="n">
-        <v>4065.956975100584</v>
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>202.2144422054449</v>
       </c>
     </row>
     <row r="11">
@@ -944,7 +1008,13 @@
         <v>64.7496602273104</v>
       </c>
       <c r="N11" t="n">
-        <v>4197.930742485422</v>
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>199.4355694088916</v>
       </c>
     </row>
     <row r="12">
@@ -990,7 +1060,13 @@
         <v>59.33114641561571</v>
       </c>
       <c r="N12" t="n">
-        <v>4087.720373588187</v>
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>197.574659682317</v>
       </c>
     </row>
     <row r="13">
@@ -1036,7 +1112,13 @@
         <v>74.01962271305338</v>
       </c>
       <c r="N13" t="n">
-        <v>4068.31172765773</v>
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>164.1116148627296</v>
       </c>
     </row>
     <row r="14">
@@ -1082,7 +1164,13 @@
         <v>56.19155054191551</v>
       </c>
       <c r="N14" t="n">
-        <v>4023.05440588169</v>
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>164.3716602580816</v>
       </c>
     </row>
     <row r="15">
@@ -1128,7 +1216,13 @@
         <v>60.83913167124846</v>
       </c>
       <c r="N15" t="n">
-        <v>3986.871127900696</v>
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>163.7783827818371</v>
       </c>
     </row>
     <row r="16">
@@ -1174,7 +1268,13 @@
         <v>68.72679874869655</v>
       </c>
       <c r="N16" t="n">
-        <v>3748.511386186304</v>
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>163.9180128741341</v>
       </c>
     </row>
     <row r="17">
@@ -1220,7 +1320,13 @@
         <v>71.46023319745946</v>
       </c>
       <c r="N17" t="n">
-        <v>3767.910383035624</v>
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>163.892797116133</v>
       </c>
     </row>
     <row r="18">
@@ -1266,7 +1372,13 @@
         <v>73.78383084577113</v>
       </c>
       <c r="N18" t="n">
-        <v>3191.512169410027</v>
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>162.2154074606115</v>
       </c>
     </row>
     <row r="19">
@@ -1312,7 +1424,13 @@
         <v>52.77043779184147</v>
       </c>
       <c r="N19" t="n">
-        <v>3544.774956055133</v>
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>165.4344616773116</v>
       </c>
     </row>
     <row r="20">
@@ -1358,7 +1476,13 @@
         <v>86.64619758351101</v>
       </c>
       <c r="N20" t="n">
-        <v>3373.23554210687</v>
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>162.1997410880113</v>
       </c>
     </row>
     <row r="21">
@@ -1404,7 +1528,13 @@
         <v>122.2219061840764</v>
       </c>
       <c r="N21" t="n">
-        <v>3555.567111029944</v>
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>164.714641473131</v>
       </c>
     </row>
     <row r="22">
@@ -1450,7 +1580,13 @@
         <v>77.47719734660033</v>
       </c>
       <c r="N22" t="n">
-        <v>3381.886907333138</v>
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>163.0742807839748</v>
       </c>
     </row>
     <row r="23">
@@ -1496,7 +1632,13 @@
         <v>99.23394723743156</v>
       </c>
       <c r="N23" t="n">
-        <v>3727.159061023223</v>
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>166.1333343704748</v>
       </c>
     </row>
     <row r="24">
@@ -1542,7 +1684,13 @@
         <v>74.30305614783227</v>
       </c>
       <c r="N24" t="n">
-        <v>3301.842029698095</v>
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>160.5257683828768</v>
       </c>
     </row>
     <row r="25">
@@ -1588,7 +1736,13 @@
         <v>101.1440896916258</v>
       </c>
       <c r="N25" t="n">
-        <v>3803.756445739256</v>
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>165.2246605928219</v>
       </c>
     </row>
     <row r="26">
@@ -1634,7 +1788,13 @@
         <v>67.68242122719734</v>
       </c>
       <c r="N26" t="n">
-        <v>3178.352993618615</v>
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>159.8686676151293</v>
       </c>
     </row>
     <row r="27">
@@ -1680,7 +1840,13 @@
         <v>90.188342932992</v>
       </c>
       <c r="N27" t="n">
-        <v>3867.777307410891</v>
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>164.8525153681946</v>
       </c>
     </row>
     <row r="28">
@@ -1726,7 +1892,13 @@
         <v>84.98821766101837</v>
       </c>
       <c r="N28" t="n">
-        <v>3815.084231792643</v>
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>168.2259443740737</v>
       </c>
     </row>
     <row r="29">
@@ -1772,7 +1944,13 @@
         <v>80.7574955541149</v>
       </c>
       <c r="N29" t="n">
-        <v>3736.892054472415</v>
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>165.587598325401</v>
       </c>
     </row>
     <row r="30">
@@ -1818,7 +1996,13 @@
         <v>87.6606971861562</v>
       </c>
       <c r="N30" t="n">
-        <v>3711.786197511692</v>
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>165.76575834836</v>
       </c>
     </row>
     <row r="31">
@@ -1864,7 +2048,13 @@
         <v>94.7900055313353</v>
       </c>
       <c r="N31" t="n">
-        <v>3764.557714120901</v>
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>165.274437621569</v>
       </c>
     </row>
     <row r="32">
@@ -1910,7 +2100,13 @@
         <v>79.64877805070986</v>
       </c>
       <c r="N32" t="n">
-        <v>3806.316120714351</v>
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>165.9987241648193</v>
       </c>
     </row>
     <row r="33">
@@ -1956,7 +2152,13 @@
         <v>71.7020256702109</v>
       </c>
       <c r="N33" t="n">
-        <v>3354.521775956297</v>
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>166.3573592233088</v>
       </c>
     </row>
     <row r="34">
@@ -2002,7 +2204,13 @@
         <v>87.42816690264013</v>
       </c>
       <c r="N34" t="n">
-        <v>3620.678795972879</v>
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>165.8185759589621</v>
       </c>
     </row>
     <row r="35">
@@ -2048,7 +2256,13 @@
         <v>74.14808028649955</v>
       </c>
       <c r="N35" t="n">
-        <v>3615.736807072276</v>
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>165.3742956319397</v>
       </c>
     </row>
     <row r="36">
@@ -2094,7 +2308,13 @@
         <v>65.61106021487467</v>
       </c>
       <c r="N36" t="n">
-        <v>3477.467738529457</v>
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>165.1605921887021</v>
       </c>
     </row>
     <row r="37">
@@ -2140,7 +2360,13 @@
         <v>79.49334316886578</v>
       </c>
       <c r="N37" t="n">
-        <v>3353.945120719724</v>
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>164.9423877152095</v>
       </c>
     </row>
     <row r="38">
@@ -2186,7 +2412,13 @@
         <v>167.8202657807309</v>
       </c>
       <c r="N38" t="n">
-        <v>3546.348302485471</v>
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>167.66095449489</v>
       </c>
     </row>
     <row r="39">
@@ -2232,7 +2464,13 @@
         <v>157.2577307368646</v>
       </c>
       <c r="N39" t="n">
-        <v>3613.671679410915</v>
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>168.9317984729927</v>
       </c>
     </row>
     <row r="40">
@@ -2258,13 +2496,11 @@
       <c r="G40" t="n">
         <v>0.117</v>
       </c>
-      <c r="H40">
-        <f>AVERAGE(Raw!AT24:AT30)</f>
-        <v/>
-      </c>
-      <c r="I40">
-        <f>AVERAGE(Raw!AU24:AU30)</f>
-        <v/>
+      <c r="H40" t="n">
+        <v>133.2502135738016</v>
+      </c>
+      <c r="I40" t="n">
+        <v>140.2467963929758</v>
       </c>
       <c r="J40" t="n">
         <v>30.14294015107496</v>
@@ -2280,7 +2516,13 @@
         <v>140.2467963929758</v>
       </c>
       <c r="N40" t="n">
-        <v>3584.314815205912</v>
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>166.9374935027656</v>
       </c>
     </row>
     <row r="41">
@@ -2326,7 +2568,13 @@
         <v>129.1137476147017</v>
       </c>
       <c r="N41" t="n">
-        <v>3666.880384615356</v>
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>168.92766161739</v>
       </c>
     </row>
     <row r="42">
@@ -2372,7 +2620,13 @@
         <v>139.2066445182724</v>
       </c>
       <c r="N42" t="n">
-        <v>3418.482993462785</v>
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>165.6683947138033</v>
       </c>
     </row>
     <row r="43">
@@ -2418,7 +2672,13 @@
         <v>131.8046234153617</v>
       </c>
       <c r="N43" t="n">
-        <v>4003.124712086958</v>
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>171.6020014244349</v>
       </c>
     </row>
     <row r="44">
@@ -2464,7 +2724,13 @@
         <v>121.4374684155773</v>
       </c>
       <c r="N44" t="n">
-        <v>3399.997061442549</v>
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>174.8395031632474</v>
       </c>
     </row>
     <row r="45">
@@ -2510,7 +2776,13 @@
         <v>131.9910514541387</v>
       </c>
       <c r="N45" t="n">
-        <v>3863.728008363844</v>
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>172.6465518325997</v>
       </c>
     </row>
     <row r="46">
@@ -2556,7 +2828,13 @@
         <v>94.13641188094392</v>
       </c>
       <c r="N46" t="n">
-        <v>3690.843493538872</v>
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>177.5393322999609</v>
       </c>
     </row>
     <row r="47">
@@ -2602,7 +2880,13 @@
         <v>114.4095735236675</v>
       </c>
       <c r="N47" t="n">
-        <v>3930.691866383889</v>
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>172.4264199714686</v>
       </c>
     </row>
     <row r="48">
@@ -2648,7 +2932,13 @@
         <v>116.5907373145101</v>
       </c>
       <c r="N48" t="n">
-        <v>3710.781390031999</v>
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>176.233713680489</v>
       </c>
     </row>
     <row r="49">
@@ -2694,7 +2984,13 @@
         <v>86.09868257519264</v>
       </c>
       <c r="N49" t="n">
-        <v>3894.89385672636</v>
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>172.3633449334573</v>
       </c>
     </row>
     <row r="50">
@@ -2740,7 +3036,13 @@
         <v>93.92845510712006</v>
       </c>
       <c r="N50" t="n">
-        <v>3757.650647285941</v>
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>175.1602631506861</v>
       </c>
     </row>
     <row r="51">
@@ -2786,7 +3088,13 @@
         <v>81.44038445604441</v>
       </c>
       <c r="N51" t="n">
-        <v>3877.924451689379</v>
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>172.029181897695</v>
       </c>
     </row>
     <row r="52">
@@ -2832,7 +3140,13 @@
         <v>100.1994679671913</v>
       </c>
       <c r="N52" t="n">
-        <v>3732.328625000007</v>
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>176.5827656244719</v>
       </c>
     </row>
     <row r="53">
@@ -2878,7 +3192,13 @@
         <v>72.34843987267851</v>
       </c>
       <c r="N53" t="n">
-        <v>3853.358918918932</v>
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>193.263088266092</v>
       </c>
     </row>
     <row r="54">
@@ -2924,7 +3244,13 @@
         <v>81.23185668953124</v>
       </c>
       <c r="N54" t="n">
-        <v>3914.654505916856</v>
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>195.4397432491899</v>
       </c>
     </row>
     <row r="55">
@@ -2970,7 +3296,13 @@
         <v>112.4842976427991</v>
       </c>
       <c r="N55" t="n">
-        <v>3678.24923847276</v>
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>175.5682666340174</v>
       </c>
     </row>
     <row r="56">
@@ -3016,7 +3348,13 @@
         <v>204.2864206380021</v>
       </c>
       <c r="N56" t="n">
-        <v>4098.97825800791</v>
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>173.0492420864555</v>
       </c>
     </row>
     <row r="57">
@@ -3062,7 +3400,13 @@
         <v>232.6257758811793</v>
       </c>
       <c r="N57" t="n">
-        <v>3630.215908396964</v>
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>175.2825882298528</v>
       </c>
     </row>
     <row r="58">
@@ -3108,7 +3452,13 @@
         <v>175.1027410735323</v>
       </c>
       <c r="N58" t="n">
-        <v>4093.795284447332</v>
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>176.3937903149738</v>
       </c>
     </row>
     <row r="59">
@@ -3154,7 +3504,13 @@
         <v>206.3427732210153</v>
       </c>
       <c r="N59" t="n">
-        <v>3427.02048879088</v>
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>174.3860262279789</v>
       </c>
     </row>
     <row r="60">
@@ -3200,7 +3556,13 @@
         <v>151.4786228879948</v>
       </c>
       <c r="N60" t="n">
-        <v>3902.540298056603</v>
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>178.8715632807744</v>
       </c>
     </row>
     <row r="61">
@@ -3246,7 +3608,13 @@
         <v>181.3829527820882</v>
       </c>
       <c r="N61" t="n">
-        <v>3462.872165236858</v>
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>173.173287159781</v>
       </c>
     </row>
     <row r="62">
@@ -3292,7 +3660,13 @@
         <v>130.7146151873327</v>
       </c>
       <c r="N62" t="n">
-        <v>3828.146626423909</v>
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>180.3467754218704</v>
       </c>
     </row>
     <row r="63">
@@ -3338,7 +3712,13 @@
         <v>125.6816892154228</v>
       </c>
       <c r="N63" t="n">
-        <v>3938.733278450377</v>
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>181.9649516308528</v>
       </c>
     </row>
     <row r="64">
@@ -3384,7 +3764,13 @@
         <v>104.6265350149353</v>
       </c>
       <c r="N64" t="n">
-        <v>3542.564317425075</v>
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>175.2376254779156</v>
       </c>
     </row>
     <row r="65">
@@ -3430,7 +3816,13 @@
         <v>122.7735645536011</v>
       </c>
       <c r="N65" t="n">
-        <v>3663.02534527097</v>
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>173.8060907418091</v>
       </c>
     </row>
     <row r="66">
@@ -3476,7 +3868,13 @@
         <v>120.871335324704</v>
       </c>
       <c r="N66" t="n">
-        <v>3858.934381221842</v>
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>175.5656427710292</v>
       </c>
     </row>
     <row r="67">
@@ -3522,7 +3920,13 @@
         <v>117.3837537338201</v>
       </c>
       <c r="N67" t="n">
-        <v>3856.669983433464</v>
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>174.8034926407652</v>
       </c>
     </row>
     <row r="68">
@@ -3568,7 +3972,13 @@
         <v>112.6569310764465</v>
       </c>
       <c r="N68" t="n">
-        <v>3627.632906295754</v>
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>174.3358927685235</v>
       </c>
     </row>
     <row r="69">
@@ -3614,7 +4024,13 @@
         <v>95.23266666666669</v>
       </c>
       <c r="N69" t="n">
-        <v>3528.622961141174</v>
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>180.2840618188942</v>
       </c>
     </row>
     <row r="70">
@@ -3660,7 +4076,13 @@
         <v>101.9636019181813</v>
       </c>
       <c r="N70" t="n">
-        <v>3700.690443068129</v>
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>175.1185922613836</v>
       </c>
     </row>
     <row r="71">
@@ -3706,7 +4128,13 @@
         <v>112.3194166666667</v>
       </c>
       <c r="N71" t="n">
-        <v>3498.133586757772</v>
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>180.7300722134197</v>
       </c>
     </row>
     <row r="72">
@@ -3752,7 +4180,13 @@
         <v>117.1886566810728</v>
       </c>
       <c r="N72" t="n">
-        <v>3960.178615240666</v>
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>177.2998132127756</v>
       </c>
     </row>
     <row r="73">
@@ -3798,7 +4232,13 @@
         <v>115.4285714285714</v>
       </c>
       <c r="N73" t="n">
-        <v>3503.511659714803</v>
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>179.0856599852061</v>
       </c>
     </row>
     <row r="74">
@@ -3844,7 +4284,13 @@
         <v>234.2549286602332</v>
       </c>
       <c r="N74" t="n">
-        <v>4070.255097826087</v>
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>177.8795019376589</v>
       </c>
     </row>
     <row r="75">
@@ -3890,7 +4336,13 @@
         <v>262.6666666666667</v>
       </c>
       <c r="N75" t="n">
-        <v>3659.720502700469</v>
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>180.0335772077534</v>
       </c>
     </row>
     <row r="76">
@@ -3936,7 +4388,13 @@
         <v>215.0020721094074</v>
       </c>
       <c r="N76" t="n">
-        <v>3792.739588413149</v>
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>177.9556268322846</v>
       </c>
     </row>
     <row r="77">
@@ -3982,7 +4440,13 @@
         <v>240.5119428571429</v>
       </c>
       <c r="N77" t="n">
-        <v>3723.489856600586</v>
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>178.3221758620086</v>
       </c>
     </row>
     <row r="78">
@@ -4028,7 +4492,13 @@
         <v>184.0033153750518</v>
       </c>
       <c r="N78" t="n">
-        <v>3813.88077370564</v>
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>178.5246481366109</v>
       </c>
     </row>
     <row r="79">
@@ -4074,7 +4544,13 @@
         <v>145.7805709362937</v>
       </c>
       <c r="N79" t="n">
-        <v>3646.069170489285</v>
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>188.0300058673498</v>
       </c>
     </row>
     <row r="80">
@@ -4120,7 +4596,13 @@
         <v>115.3137162663583</v>
       </c>
       <c r="N80" t="n">
-        <v>3915.476017578744</v>
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>188.0487657627732</v>
       </c>
     </row>
     <row r="81">
@@ -4166,7 +4648,13 @@
         <v>125.0402886306515</v>
       </c>
       <c r="N81" t="n">
-        <v>3905.003742592787</v>
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>186.4076929575676</v>
       </c>
     </row>
     <row r="82">
@@ -4212,7 +4700,13 @@
         <v>107.9667781165188</v>
       </c>
       <c r="N82" t="n">
-        <v>3622.320474943878</v>
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>185.1922507013823</v>
       </c>
     </row>
     <row r="83">
@@ -4258,7 +4752,13 @@
         <v>114.5533282414514</v>
       </c>
       <c r="N83" t="n">
-        <v>3604.577615370479</v>
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>183.6984480892077</v>
       </c>
     </row>
     <row r="84">
@@ -4304,7 +4804,13 @@
         <v>132.0913617265441</v>
       </c>
       <c r="N84" t="n">
-        <v>3789.95878639787</v>
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>178.6832180218116</v>
       </c>
     </row>
     <row r="85">
@@ -4350,7 +4856,13 @@
         <v>118.3913968941455</v>
       </c>
       <c r="N85" t="n">
-        <v>3982.23143802006</v>
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>179.845618718587</v>
       </c>
     </row>
     <row r="86">
@@ -4396,7 +4908,13 @@
         <v>129.168082625354</v>
       </c>
       <c r="N86" t="n">
-        <v>4014.181129611472</v>
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>179.0640309537618</v>
       </c>
     </row>
     <row r="87">
@@ -4442,7 +4960,13 @@
         <v>111.971764117941</v>
       </c>
       <c r="N87" t="n">
-        <v>3989.271911812395</v>
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>178.7443230385731</v>
       </c>
     </row>
     <row r="88">
@@ -4488,7 +5012,13 @@
         <v>96.21922372147259</v>
       </c>
       <c r="N88" t="n">
-        <v>3990.231843162123</v>
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>178.189072955256</v>
       </c>
     </row>
     <row r="89">
@@ -4534,7 +5064,13 @@
         <v>116.2807</v>
       </c>
       <c r="N89" t="n">
-        <v>3663.243893343292</v>
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>190.3672983198846</v>
       </c>
     </row>
     <row r="90">
@@ -4580,7 +5116,13 @@
         <v>94.55328</v>
       </c>
       <c r="N90" t="n">
-        <v>3685.998120728948</v>
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>191.2244703014589</v>
       </c>
     </row>
     <row r="91">
@@ -4626,7 +5168,13 @@
         <v>110.6067250595584</v>
       </c>
       <c r="N91" t="n">
-        <v>3957.212329795213</v>
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>170.4395792858829</v>
       </c>
     </row>
     <row r="92">
@@ -4672,7 +5220,13 @@
         <v>294.9098243948742</v>
       </c>
       <c r="N92" t="n">
-        <v>3275.648690408896</v>
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>164.2948405981972</v>
       </c>
     </row>
     <row r="93">
@@ -4718,7 +5272,13 @@
         <v>296.5315570515936</v>
       </c>
       <c r="N93" t="n">
-        <v>3760.25264714883</v>
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>173.0138069647003</v>
       </c>
     </row>
     <row r="94">
@@ -4764,7 +5324,13 @@
         <v>260.0299952539155</v>
       </c>
       <c r="N94" t="n">
-        <v>3302.554294185168</v>
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>162.7876678716447</v>
       </c>
     </row>
     <row r="95">
@@ -4810,7 +5376,13 @@
         <v>272.8044470256368</v>
       </c>
       <c r="N95" t="n">
-        <v>3673.219986819793</v>
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>170.0245042977531</v>
       </c>
     </row>
     <row r="96">
@@ -4856,7 +5428,13 @@
         <v>268.3675182008423</v>
       </c>
       <c r="N96" t="n">
-        <v>3506.49680175019</v>
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>169.5588997484363</v>
       </c>
     </row>
     <row r="97">
@@ -4902,7 +5480,13 @@
         <v>235.8097446856924</v>
       </c>
       <c r="N97" t="n">
-        <v>3273.720818790664</v>
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>169.6571559835494</v>
       </c>
     </row>
     <row r="98">
@@ -4948,7 +5532,13 @@
         <v>193.5552077404667</v>
       </c>
       <c r="N98" t="n">
-        <v>3750.065799641865</v>
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>167.4936054849216</v>
       </c>
     </row>
     <row r="99">
@@ -4994,7 +5584,13 @@
         <v>189.5731040492127</v>
       </c>
       <c r="N99" t="n">
-        <v>3259.429566398288</v>
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>168.0888769749866</v>
       </c>
     </row>
     <row r="100">
@@ -5040,7 +5636,13 @@
         <v>146.1204349269588</v>
       </c>
       <c r="N100" t="n">
-        <v>3991.034179321823</v>
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>172.2341257100592</v>
       </c>
     </row>
     <row r="101">
@@ -5086,7 +5688,13 @@
         <v>168.5831354506203</v>
       </c>
       <c r="N101" t="n">
-        <v>3266.139835137543</v>
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>168.1650760755083</v>
       </c>
     </row>
     <row r="102">
@@ -5132,7 +5740,13 @@
         <v>147.4933598937583</v>
       </c>
       <c r="N102" t="n">
-        <v>4017.882815584422</v>
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>170.3489412327481</v>
       </c>
     </row>
     <row r="103">
@@ -5178,7 +5792,13 @@
         <v>125.5320775644953</v>
       </c>
       <c r="N103" t="n">
-        <v>3269.816514981086</v>
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>168.3600461050797</v>
       </c>
     </row>
     <row r="104">
@@ -5224,7 +5844,13 @@
         <v>160.0660216277746</v>
       </c>
       <c r="N104" t="n">
-        <v>3985.114723032084</v>
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>169.8117537588455</v>
       </c>
     </row>
     <row r="105">
@@ -5270,7 +5896,13 @@
         <v>146.2713590084108</v>
       </c>
       <c r="N105" t="n">
-        <v>3883.041503523861</v>
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>171.2899615421531</v>
       </c>
     </row>
     <row r="106">
@@ -5316,7 +5948,13 @@
         <v>130.094414893617</v>
       </c>
       <c r="N106" t="n">
-        <v>3529.095531252945</v>
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>172.2508988520746</v>
       </c>
     </row>
     <row r="107">
@@ -5362,7 +6000,13 @@
         <v>123.9349143026005</v>
       </c>
       <c r="N107" t="n">
-        <v>3737.669427359479</v>
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>174.9901456068946</v>
       </c>
     </row>
     <row r="108">
@@ -5408,7 +6052,13 @@
         <v>113.1862651975684</v>
       </c>
       <c r="N108" t="n">
-        <v>3802.472276350764</v>
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>174.0419873295182</v>
       </c>
     </row>
     <row r="109">
@@ -5454,7 +6104,13 @@
         <v>123.7048703457447</v>
       </c>
       <c r="N109" t="n">
-        <v>3597.26451291254</v>
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>173.0278840656405</v>
       </c>
     </row>
     <row r="110">
@@ -5500,7 +6156,13 @@
         <v>151.703125</v>
       </c>
       <c r="N110" t="n">
-        <v>3483.990679094537</v>
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>172.4772043605039</v>
       </c>
     </row>
     <row r="111">
@@ -5546,7 +6208,13 @@
         <v>162.4157651694777</v>
       </c>
       <c r="N111" t="n">
-        <v>3418.522030497596</v>
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>174.3642834825657</v>
       </c>
     </row>
   </sheetData>
